--- a/dados/Make_Monetaria_REAL.xlsx
+++ b/dados/Make_Monetaria_REAL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/768ce10d4f3360c7/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\Documents\dev_2026\gd_impacta_mg\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA19524E-7951-4CFF-ABFA-47A144DDBBED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6D7598-236D-4572-BE7B-4C2E9488C1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{BD14A59D-08AE-458F-8E9E-A36A88EBC844}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="5" xr2:uid="{BD14A59D-08AE-458F-8E9E-A36A88EBC844}"/>
   </bookViews>
   <sheets>
     <sheet name="Agropec" sheetId="6" r:id="rId1"/>
@@ -24,6 +24,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -246,7 +257,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.0000%"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,14 +293,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -295,9 +319,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -335,7 +359,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -441,7 +465,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -583,7 +607,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -591,14 +615,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D994BB5-0A33-4589-9A5B-A2E1612255D1}">
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>67</v>
       </c>
@@ -609,7 +633,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -623,7 +647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -641,7 +665,7 @@
         <v>-15.397899999999936</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -659,7 +683,7 @@
         <v>16.095548999999892</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -677,7 +701,7 @@
         <v>8.1365890000000149</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -695,7 +719,7 @@
         <v>-3.5383870000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -713,7 +737,7 @@
         <v>4.8348580000000254</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -731,7 +755,7 @@
         <v>-24.574727000000166</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -749,7 +773,7 @@
         <v>-5.214191000000028</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -767,7 +791,7 @@
         <v>-57.104503999999906</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -785,7 +809,7 @@
         <v>7.627584000000013</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -803,7 +827,7 @@
         <v>21.319612000000006</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -821,7 +845,7 @@
         <v>8.1829999999172287E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -839,7 +863,7 @@
         <v>4.175946999999951</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -857,7 +881,7 @@
         <v>16.847514000000047</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -875,7 +899,7 @@
         <v>3.6139320000000907</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -893,7 +917,7 @@
         <v>-4.6903330000000096</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -911,7 +935,7 @@
         <v>8.5963070000000243</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -929,7 +953,7 @@
         <v>10.277596000000017</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -947,7 +971,7 @@
         <v>4.6850179999999852</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -965,7 +989,7 @@
         <v>34.798625000000015</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -983,7 +1007,7 @@
         <v>11.378749999999968</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -1001,7 +1025,7 @@
         <v>-30.027001999999811</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -1019,7 +1043,7 @@
         <v>7.4584910000000946</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -1037,7 +1061,7 @@
         <v>-3.8607999999996423E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -1055,7 +1079,7 @@
         <v>-0.54800299999999424</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -1073,7 +1097,7 @@
         <v>4.2825249999999642</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -1091,7 +1115,7 @@
         <v>-6.098594999999932</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -1109,7 +1133,7 @@
         <v>7.0527940000000058</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -1127,7 +1151,7 @@
         <v>-0.53293699999994715</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -1145,7 +1169,7 @@
         <v>-8.935271000000057</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -1163,7 +1187,7 @@
         <v>17.497444999999971</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -1181,7 +1205,7 @@
         <v>28.635672999999997</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -1199,7 +1223,7 @@
         <v>-1.0724259999999504</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -1217,7 +1241,7 @@
         <v>-2.4332930000000488</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -1235,7 +1259,7 @@
         <v>0.8262409999999818</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -1253,7 +1277,7 @@
         <v>6.2344369999999856</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -1271,7 +1295,7 @@
         <v>9.4789729999999963</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1289,7 +1313,7 @@
         <v>20.254621000000043</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -1307,7 +1331,7 @@
         <v>-12.489901000000032</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -1325,7 +1349,7 @@
         <v>12.726578000000018</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -1343,7 +1367,7 @@
         <v>-8.5189100000000053</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -1361,7 +1385,7 @@
         <v>-2.8872010000000046</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -1379,7 +1403,7 @@
         <v>3.57415600000013</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -1397,7 +1421,7 @@
         <v>18.777806999999939</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -1415,7 +1439,7 @@
         <v>-3.4487519999997858</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -1433,7 +1457,7 @@
         <v>-9.2659670000002734</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -1451,7 +1475,7 @@
         <v>5.8036539999999945</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -1469,7 +1493,7 @@
         <v>3.8573740000000072</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -1487,7 +1511,7 @@
         <v>13.066484000000003</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -1505,7 +1529,7 @@
         <v>-15.477163999999902</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -1523,7 +1547,7 @@
         <v>-15.353380999999899</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -1541,7 +1565,7 @@
         <v>-8.781472999999778</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -1559,7 +1583,7 @@
         <v>0.57289800000000923</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -1577,7 +1601,7 @@
         <v>5.1314199999999914</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -1595,7 +1619,7 @@
         <v>-3.9522379999999657</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -1613,7 +1637,7 @@
         <v>9.5214290000000119</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -1631,7 +1655,7 @@
         <v>13.255181999999991</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -1649,7 +1673,7 @@
         <v>-2.3109750000000986</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -1667,7 +1691,7 @@
         <v>29.472150000000056</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -1685,7 +1709,7 @@
         <v>20.313808999999992</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -1703,7 +1727,7 @@
         <v>9.6802830000000313</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -1721,7 +1745,7 @@
         <v>11.442891000000031</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -1739,7 +1763,7 @@
         <v>30.066896000000042</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -1757,7 +1781,7 @@
         <v>-99.879863000000114</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -1775,7 +1799,7 @@
         <v>-40.297011999999995</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -1793,7 +1817,7 @@
         <v>27.402042999999821</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -1807,8 +1831,26 @@
         <v>920.08900000000006</v>
       </c>
       <c r="G68">
-        <f t="shared" ref="G68:G69" si="1">E68-B68</f>
+        <f t="shared" ref="G68" si="1">E68-B68</f>
         <v>15.293712000000028</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B70">
+        <f>SUM(B3:B68)</f>
+        <v>75381.025983999993</v>
+      </c>
+      <c r="E70">
+        <f>SUM(E3:E68)</f>
+        <v>75482.233000000007</v>
+      </c>
+      <c r="G70">
+        <f>SUM(G3:G68)</f>
+        <v>101.20701600000046</v>
+      </c>
+      <c r="H70" s="1">
+        <f>G70/B70</f>
+        <v>1.3426059764891256E-3</v>
       </c>
     </row>
   </sheetData>
@@ -1818,14 +1860,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{100931DE-165D-40DC-ADFB-F4ABF15FE41E}">
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>67</v>
       </c>
@@ -1836,7 +1878,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1850,7 +1892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1868,7 +1910,7 @@
         <v>0.70662100000000017</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1886,7 +1928,7 @@
         <v>2.6397769999999952</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1904,7 +1946,7 @@
         <v>0.29518999999999984</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1922,7 +1964,7 @@
         <v>4.0325000000000166E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1940,7 +1982,7 @@
         <v>0.34829099999999968</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1958,7 +2000,7 @@
         <v>9.2439159999999561</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1976,7 +2018,7 @@
         <v>1.0926949999999991</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1994,7 +2036,7 @@
         <v>257.36285900000075</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2012,7 +2054,7 @@
         <v>0.54858000000000118</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2030,7 +2072,7 @@
         <v>1.3432659999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2048,7 +2090,7 @@
         <v>0.50696599999999847</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -2066,7 +2108,7 @@
         <v>0.52588199999999929</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -2084,7 +2126,7 @@
         <v>0.50673399999999802</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2102,7 +2144,7 @@
         <v>3.1690700000000049</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2120,7 +2162,7 @@
         <v>3.0927800000000047</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -2138,7 +2180,7 @@
         <v>28.080728999999792</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -2156,7 +2198,7 @@
         <v>0.31683600000000034</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2174,7 +2216,7 @@
         <v>0.31422300000000014</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2192,7 +2234,7 @@
         <v>17.707690000000071</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -2210,7 +2252,7 @@
         <v>1.4910420000000073</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2228,7 +2270,7 @@
         <v>2.2040920000000028</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -2246,7 +2288,7 @@
         <v>1.7972429999999946</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2264,7 +2306,7 @@
         <v>0.22089099999999995</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -2282,7 +2324,7 @@
         <v>0.41702300000000037</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2300,7 +2342,7 @@
         <v>24.808366999999862</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -2318,7 +2360,7 @@
         <v>35.053638999999976</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -2336,7 +2378,7 @@
         <v>6.8059829999999693</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -2354,7 +2396,7 @@
         <v>1.5251970000000057</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -2372,7 +2414,7 @@
         <v>1.3111539999999948</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -2390,7 +2432,7 @@
         <v>4.6921870000000041</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -2408,7 +2450,7 @@
         <v>0.58122099999999932</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -2426,7 +2468,7 @@
         <v>6.513225000000034</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -2444,7 +2486,7 @@
         <v>0.73173599999999794</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -2462,7 +2504,7 @@
         <v>3.3524490000000071</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -2480,7 +2522,7 @@
         <v>8.6526000000000103E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -2498,7 +2540,7 @@
         <v>1.6793650000000042</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -2516,7 +2558,7 @@
         <v>3.8611410000000035</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -2534,7 +2576,7 @@
         <v>0.38056899999999949</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -2552,7 +2594,7 @@
         <v>1.4047319999999957</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -2570,7 +2612,7 @@
         <v>35.548082000000022</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -2588,7 +2630,7 @@
         <v>1.4272690000000026</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -2606,7 +2648,7 @@
         <v>9.0710679999999684</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -2624,7 +2666,7 @@
         <v>3.3043499999999995</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -2642,7 +2684,7 @@
         <v>1.0084919999999968</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -2660,7 +2702,7 @@
         <v>1.2655770000000004</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -2678,7 +2720,7 @@
         <v>7.1019000000000165E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -2696,7 +2738,7 @@
         <v>0.2612710000000007</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -2714,7 +2756,7 @@
         <v>1.2734869999999994</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -2732,7 +2774,7 @@
         <v>0.11944599999999994</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -2750,7 +2792,7 @@
         <v>6.4311860000000252</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -2768,7 +2810,7 @@
         <v>0.68833099999999803</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -2786,7 +2828,7 @@
         <v>4.5270779999999888</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -2804,7 +2846,7 @@
         <v>1.0190269999999995</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -2822,7 +2864,7 @@
         <v>0.89118899999999712</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -2840,7 +2882,7 @@
         <v>4.4994740000000064</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -2858,7 +2900,7 @@
         <v>0.64461000000000013</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -2876,7 +2918,7 @@
         <v>3.5566129999999987</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -2894,7 +2936,7 @@
         <v>3.7055960000000141</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -2912,7 +2954,7 @@
         <v>0.52312200000000075</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -2930,7 +2972,7 @@
         <v>3.2072710000000058</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -2948,7 +2990,7 @@
         <v>2.0188089999999903</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -2966,7 +3008,7 @@
         <v>8.371921000000043</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -2984,7 +3026,7 @@
         <v>13.227432000000022</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -3002,7 +3044,7 @@
         <v>1.3584639999999979</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -3020,7 +3062,7 @@
         <v>3.4702659999999952</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -3034,8 +3076,26 @@
         <v>18.116</v>
       </c>
       <c r="G68">
-        <f t="shared" ref="G68:G69" si="1">E68-B68</f>
+        <f t="shared" ref="G68" si="1">E68-B68</f>
         <v>0.51668199999999942</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B70">
+        <f>SUM(B3:B68)</f>
+        <v>23572.286656000015</v>
+      </c>
+      <c r="E70">
+        <f>SUM(E3:E68)</f>
+        <v>24111.054000000011</v>
+      </c>
+      <c r="G70">
+        <f>SUM(G3:G68)</f>
+        <v>538.76734400000055</v>
+      </c>
+      <c r="H70" s="1">
+        <f>G70/B70</f>
+        <v>2.2855964373013613E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3045,13 +3105,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B10B9CA-2581-4862-830B-8C8BBBD7F143}">
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>67</v>
       </c>
@@ -3062,7 +3122,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3076,7 +3136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3094,7 +3154,7 @@
         <v>6.1371630000000152</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -3112,7 +3172,7 @@
         <v>40.727401999999984</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3130,7 +3190,7 @@
         <v>6.7572389999999984</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3148,7 +3208,7 @@
         <v>-0.93825099999999395</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -3166,7 +3226,7 @@
         <v>5.2364010000000007</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3184,7 +3244,7 @@
         <v>109.01675400000022</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -3202,7 +3262,7 @@
         <v>38.098406999999952</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -3220,7 +3280,7 @@
         <v>63.874938000008115</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3238,7 +3298,7 @@
         <v>111.09676200000013</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -3256,7 +3316,7 @@
         <v>34.799191000000064</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -3274,7 +3334,7 @@
         <v>7.8475240000000213</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -3292,7 +3352,7 @@
         <v>21.333900999999969</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -3310,7 +3370,7 @@
         <v>23.902124000000015</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -3328,7 +3388,7 @@
         <v>23.687167999999929</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -3346,7 +3406,7 @@
         <v>5.1594059999999899</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -3364,7 +3424,7 @@
         <v>224.76000400000066</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -3382,7 +3442,7 @@
         <v>15.317418000000032</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -3400,7 +3460,7 @@
         <v>5.611108999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -3418,7 +3478,7 @@
         <v>220.24198200000001</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -3436,7 +3496,7 @@
         <v>38.464099000000033</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -3454,7 +3514,7 @@
         <v>-21.439399000000094</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -3472,7 +3532,7 @@
         <v>47.775827000000049</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -3490,7 +3550,7 @@
         <v>4.6047929999999724</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -3508,7 +3568,7 @@
         <v>10.456053999999995</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -3526,7 +3586,7 @@
         <v>295.93273399999998</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -3544,7 +3604,7 @@
         <v>189.16498400000091</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -3562,7 +3622,7 @@
         <v>55.218935000000101</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -3580,7 +3640,7 @@
         <v>-9.464870000000019</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -3598,7 +3658,7 @@
         <v>33.229572999999959</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -3616,7 +3676,7 @@
         <v>18.718543000000011</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -3634,7 +3694,7 @@
         <v>24.60093599999999</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -3652,7 +3712,7 @@
         <v>257.15960199999972</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -3670,7 +3730,7 @@
         <v>3.8736390000000256</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -3688,7 +3748,7 @@
         <v>44.380453999999872</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -3706,7 +3766,7 @@
         <v>2.6797809999999984</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -3724,7 +3784,7 @@
         <v>-37.250847999999678</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -3742,7 +3802,7 @@
         <v>21.745725999999991</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -3760,7 +3820,7 @@
         <v>0.92116899999999191</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -3778,7 +3838,7 @@
         <v>16.895146000000011</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -3796,7 +3856,7 @@
         <v>118.51220300000023</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -3814,7 +3874,7 @@
         <v>50.65806299999997</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -3832,7 +3892,7 @@
         <v>-9.0718030000002727</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -3850,7 +3910,7 @@
         <v>52.42726800000014</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -3868,7 +3928,7 @@
         <v>42.898275999999896</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -3886,7 +3946,7 @@
         <v>31.495351999999912</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -3904,7 +3964,7 @@
         <v>1.1794329999999995</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -3922,7 +3982,7 @@
         <v>4.7308210000000059</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -3940,7 +4000,7 @@
         <v>102.16077599999994</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -3958,7 +4018,7 @@
         <v>9.1544529999999895</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -3976,7 +4036,7 @@
         <v>105.810473</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -3994,7 +4054,7 @@
         <v>10.250215999999995</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -4012,7 +4072,7 @@
         <v>2.2426909999994677</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -4030,7 +4090,7 @@
         <v>31.83336700000001</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -4048,7 +4108,7 @@
         <v>-31.15640099999996</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -4066,7 +4126,7 @@
         <v>29.716846000000032</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -4084,7 +4144,7 @@
         <v>13.352999999999952</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -4102,7 +4162,7 @@
         <v>35.779254000000037</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -4120,7 +4180,7 @@
         <v>89.094117000000551</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -4138,7 +4198,7 @@
         <v>22.866052000000025</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -4156,7 +4216,7 @@
         <v>398.50832799999989</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -4174,7 +4234,7 @@
         <v>38.130885000000035</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -4192,7 +4252,7 @@
         <v>71.315296999999191</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -4210,7 +4270,7 @@
         <v>71.099641000000702</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -4228,7 +4288,7 @@
         <v>23.459781000000021</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -4246,7 +4306,7 @@
         <v>49.640382999999929</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -4260,8 +4320,26 @@
         <v>344.50900000000001</v>
       </c>
       <c r="G68">
-        <f t="shared" ref="G68:G69" si="1">E68-B68</f>
+        <f t="shared" ref="G68" si="1">E68-B68</f>
         <v>12.387357000000009</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B70">
+        <f>SUM(B3:B68)</f>
+        <v>234961.79335100003</v>
+      </c>
+      <c r="E70">
+        <f>SUM(E3:E68)</f>
+        <v>238300.60300000006</v>
+      </c>
+      <c r="G70">
+        <f>SUM(G3:G68)</f>
+        <v>3338.8096490000098</v>
+      </c>
+      <c r="H70" s="1">
+        <f>G70/B70</f>
+        <v>1.4210010918721136E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4271,10 +4349,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D3FF3E-F6F1-480A-99D1-C389F81151FA}">
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>67</v>
       </c>
@@ -4285,7 +4363,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4299,7 +4377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4317,7 +4395,7 @@
         <v>51.218380999999908</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -4335,7 +4413,7 @@
         <v>35.643229999999676</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4353,7 +4431,7 @@
         <v>44.265617999999904</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -4371,7 +4449,7 @@
         <v>32.436840000000075</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -4389,7 +4467,7 @@
         <v>36.63275299999998</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -4407,7 +4485,7 @@
         <v>140.20733999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -4425,7 +4503,7 @@
         <v>44.994258000000173</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -4443,7 +4521,7 @@
         <v>954.17162499998813</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -4461,7 +4539,7 @@
         <v>48.779860000000099</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -4479,7 +4557,7 @@
         <v>140.48760399999992</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -4497,7 +4575,7 @@
         <v>69.497316000000183</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -4515,7 +4593,7 @@
         <v>49.005120000000034</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -4533,7 +4611,7 @@
         <v>34.676159999999982</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -4551,7 +4629,7 @@
         <v>60.915126999999757</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -4569,7 +4647,7 @@
         <v>10.447750000000042</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -4587,7 +4665,7 @@
         <v>90.478684000000612</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -4605,7 +4683,7 @@
         <v>143.17855899999995</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -4623,7 +4701,7 @@
         <v>22.903278</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -4641,7 +4719,7 @@
         <v>405.95596099999966</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -4659,7 +4737,7 @@
         <v>178.48912699999983</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -4677,7 +4755,7 @@
         <v>153.7345779999996</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -4695,7 +4773,7 @@
         <v>107.35473399999955</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -4713,7 +4791,7 @@
         <v>4.2420269999999931</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -4731,7 +4809,7 @@
         <v>27.199965999999904</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -4749,7 +4827,7 @@
         <v>300.30602300000101</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -4767,7 +4845,7 @@
         <v>255.74157800000103</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -4785,7 +4863,7 @@
         <v>50.854667000000063</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -4803,7 +4881,7 @@
         <v>34.567980000000261</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -4821,7 +4899,7 @@
         <v>69.200003999999808</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -4839,7 +4917,7 @@
         <v>47.120327999999972</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -4857,7 +4935,7 @@
         <v>29.049474999999802</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -4875,7 +4953,7 @@
         <v>-5.2457969999995839</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -4893,7 +4971,7 @@
         <v>101.91579299999967</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -4911,7 +4989,7 @@
         <v>66.304278999999951</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -4929,7 +5007,7 @@
         <v>8.8082670000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -4947,7 +5025,7 @@
         <v>596.4499450000003</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -4965,7 +5043,7 @@
         <v>96.534405999999763</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -4983,7 +5061,7 @@
         <v>2.1730890000001182</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -5001,7 +5079,7 @@
         <v>30.466714000000138</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -5019,7 +5097,7 @@
         <v>112.87415599999986</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -5037,7 +5115,7 @@
         <v>50.949256000000332</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -5055,7 +5133,7 @@
         <v>425.7620509999997</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -5073,7 +5151,7 @@
         <v>105.18364799999972</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -5091,7 +5169,7 @@
         <v>195.83370699999978</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -5109,7 +5187,7 @@
         <v>155.74695500000007</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -5127,7 +5205,7 @@
         <v>0.46634399999999232</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -5145,7 +5223,7 @@
         <v>5.853334000000018</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -5163,7 +5241,7 @@
         <v>175.42017499999997</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -5181,7 +5259,7 @@
         <v>164.56504900000004</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -5199,7 +5277,7 @@
         <v>124.06386700000076</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -5217,7 +5295,7 @@
         <v>55.917985000000044</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -5235,7 +5313,7 @@
         <v>-63.660343999999895</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -5253,7 +5331,7 @@
         <v>153.60456599999998</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -5271,7 +5349,7 @@
         <v>59.242904000000181</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -5289,7 +5367,7 @@
         <v>-6.948989999999867</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -5307,7 +5385,7 @@
         <v>71.683883000000151</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -5325,7 +5403,7 @@
         <v>123.05119900000045</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -5343,7 +5421,7 @@
         <v>528.27481299999999</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -5361,7 +5439,7 @@
         <v>108.52161899999965</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -5379,7 +5457,7 @@
         <v>58.672123000000056</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -5397,7 +5475,7 @@
         <v>109.36931599999934</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -5415,7 +5493,7 @@
         <v>54.964523000000554</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -5433,7 +5511,7 @@
         <v>247.13482799999838</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -5451,7 +5529,7 @@
         <v>39.938332000000173</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -5469,7 +5547,7 @@
         <v>215.94039100000009</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -5483,8 +5561,26 @@
         <v>2543.3580000000002</v>
       </c>
       <c r="G68">
-        <f t="shared" ref="G68:G69" si="1">E68-B68</f>
+        <f t="shared" ref="G68" si="1">E68-B68</f>
         <v>26.051604000000225</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B70">
+        <f>SUM(B3:B68)</f>
+        <v>426918.35705899994</v>
+      </c>
+      <c r="E70">
+        <f>SUM(E3:E68)</f>
+        <v>434787.99699999992</v>
+      </c>
+      <c r="G70">
+        <f>SUM(G3:G68)</f>
+        <v>7869.6399409999922</v>
+      </c>
+      <c r="H70" s="1">
+        <f>G70/B70</f>
+        <v>1.8433594646089232E-2</v>
       </c>
     </row>
   </sheetData>
@@ -5494,10 +5590,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03B187FE-E1B4-47D4-AB1D-6743156F5231}">
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>67</v>
       </c>
@@ -5508,7 +5604,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5522,7 +5618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5540,7 +5636,7 @@
         <v>5.9032660000000021</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -5558,7 +5654,7 @@
         <v>25.836694999999963</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -5576,7 +5672,7 @@
         <v>8.4019949999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -5594,7 +5690,7 @@
         <v>2.8736149999999867</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -5612,7 +5708,7 @@
         <v>3.1178000000000168</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -5630,7 +5726,7 @@
         <v>25.586055000000215</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -5648,7 +5744,7 @@
         <v>16.411073000000101</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -5666,7 +5762,7 @@
         <v>639.30320299999948</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -5684,7 +5780,7 @@
         <v>4.5023809999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -5702,7 +5798,7 @@
         <v>26.665418000000045</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -5720,7 +5816,7 @@
         <v>9.0838210000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -5738,7 +5834,7 @@
         <v>10.286980999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -5756,7 +5852,7 @@
         <v>19.722759999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -5774,7 +5870,7 @@
         <v>16.499692000000096</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -5792,7 +5888,7 @@
         <v>3.1844420000000184</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -5810,7 +5906,7 @@
         <v>30.91431399999999</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -5828,7 +5924,7 @@
         <v>19.082084000000009</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -5846,7 +5942,7 @@
         <v>5.3320960000000071</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -5864,7 +5960,7 @@
         <v>108.42119000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -5882,7 +5978,7 @@
         <v>21.820268999999939</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -5900,7 +5996,7 @@
         <v>24.940151000000014</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -5918,7 +6014,7 @@
         <v>59.596850000000131</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -5936,7 +6032,7 @@
         <v>0.6441119999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -5954,7 +6050,7 @@
         <v>6.3550720000000069</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -5972,7 +6068,7 @@
         <v>78.135818999999856</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -5990,7 +6086,7 @@
         <v>43.141000000000076</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -6008,7 +6104,7 @@
         <v>6.0234859999999912</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -6026,7 +6122,7 @@
         <v>7.9038679999999886</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -6044,7 +6140,7 @@
         <v>16.583800999999994</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -6062,7 +6158,7 @@
         <v>21.689024000000018</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -6080,7 +6176,7 @@
         <v>10.691198999999983</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -6098,7 +6194,7 @@
         <v>94.89828099999977</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -6116,7 +6212,7 @@
         <v>13.296396000000016</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -6134,7 +6230,7 @@
         <v>26.569254999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -6152,7 +6248,7 @@
         <v>2.9268619999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -6170,7 +6266,7 @@
         <v>59.197150999999849</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -6188,7 +6284,7 @@
         <v>15.979679000000033</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -6206,7 +6302,7 @@
         <v>2.1211400000000253</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -6224,7 +6320,7 @@
         <v>10.947200000000009</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -6242,7 +6338,7 @@
         <v>23.299912000000177</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -6260,7 +6356,7 @@
         <v>17.045003000000008</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -6278,7 +6374,7 @@
         <v>23.212895000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -6296,7 +6392,7 @@
         <v>21.205263000000059</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -6314,7 +6410,7 @@
         <v>39.808339000000046</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -6332,7 +6428,7 @@
         <v>31.519511999999963</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -6350,7 +6446,7 @@
         <v>1.7491210000000024</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -6368,7 +6464,7 @@
         <v>0.58243200000001139</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -6386,7 +6482,7 @@
         <v>19.398635000000013</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -6404,7 +6500,7 @@
         <v>9.219268999999997</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -6422,7 +6518,7 @@
         <v>43.033284999999978</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -6440,7 +6536,7 @@
         <v>10.468615999999997</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -6458,7 +6554,7 @@
         <v>37.870265999999901</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -6476,7 +6572,7 @@
         <v>19.530796000000009</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -6494,7 +6590,7 @@
         <v>9.6240760000000023</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -6512,7 +6608,7 @@
         <v>13.800670000000025</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -6530,7 +6626,7 @@
         <v>13.963107000000036</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -6548,7 +6644,7 @@
         <v>39.147836999999981</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -6566,7 +6662,7 @@
         <v>53.557027000000062</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -6584,7 +6680,7 @@
         <v>17.970197999999982</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -6602,7 +6698,7 @@
         <v>11.709164999999985</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -6620,7 +6716,7 @@
         <v>18.122367000000054</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -6638,7 +6734,7 @@
         <v>71.107301000000007</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -6656,7 +6752,7 @@
         <v>120.2353949999997</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -6674,7 +6770,7 @@
         <v>8.7495309999999904</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -6692,7 +6788,7 @@
         <v>67.718783999999914</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -6706,8 +6802,26 @@
         <v>445.214</v>
       </c>
       <c r="G68">
-        <f t="shared" ref="G68:G69" si="1">E68-B68</f>
+        <f t="shared" ref="G68" si="1">E68-B68</f>
         <v>14.026072999999997</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B70">
+        <f>SUM(B3:B68)</f>
+        <v>78888.085628999994</v>
+      </c>
+      <c r="E70">
+        <f>SUM(E3:E68)</f>
+        <v>81150.35000000002</v>
+      </c>
+      <c r="G70">
+        <f>SUM(G3:G68)</f>
+        <v>2262.2643709999993</v>
+      </c>
+      <c r="H70" s="1">
+        <f>G70/B70</f>
+        <v>2.8676882611135008E-2</v>
       </c>
     </row>
   </sheetData>
@@ -6717,10 +6831,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA1CE2D6-43D5-407E-9C7F-4405C5AC1CDD}">
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>67</v>
       </c>
@@ -6731,7 +6845,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6745,7 +6859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6763,7 +6877,7 @@
         <v>0.50585999999999842</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -6781,7 +6895,7 @@
         <v>4.9190100000000143</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6799,7 +6913,7 @@
         <v>-6.462799999999902E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -6817,7 +6931,7 @@
         <v>-0.61120799999999775</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -6835,7 +6949,7 @@
         <v>0.58126700000000397</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -6853,7 +6967,7 @@
         <v>0.93213600000001406</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -6871,7 +6985,7 @@
         <v>1.7833339999999964</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -6889,7 +7003,7 @@
         <v>59.920234000000164</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -6907,7 +7021,7 @@
         <v>0.37960600000000255</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -6925,7 +7039,7 @@
         <v>2.6465819999999667</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -6943,7 +7057,7 @@
         <v>-1.4682410000000061</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -6961,7 +7075,7 @@
         <v>1.9469890000000021</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -6979,7 +7093,7 @@
         <v>2.4045009999999962</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -6997,7 +7111,7 @@
         <v>-0.60676100000000588</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -7015,7 +7129,7 @@
         <v>-6.8180999999999159E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -7033,7 +7147,7 @@
         <v>5.0165869999999586</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -7051,7 +7165,7 @@
         <v>0.11510600000001148</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -7069,7 +7183,7 @@
         <v>0.11306400000000139</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -7087,7 +7201,7 @@
         <v>15.828528000000006</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -7105,7 +7219,7 @@
         <v>2.0900690000000282</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -7123,7 +7237,7 @@
         <v>-5.9995480000000043</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -7141,7 +7255,7 @@
         <v>9.2544729999999618</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -7159,7 +7273,7 @@
         <v>4.709199999999969E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -7177,7 +7291,7 @@
         <v>1.2151380000000103</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -7195,7 +7309,7 @@
         <v>16.561173999999937</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -7213,7 +7327,7 @@
         <v>8.2357499999999959</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -7231,7 +7345,7 @@
         <v>-0.70226600000000872</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -7249,7 +7363,7 @@
         <v>0.38435100000000944</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -7267,7 +7381,7 @@
         <v>0.43441000000001395</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -7285,7 +7399,7 @@
         <v>2.6539229999999918</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -7303,7 +7417,7 @@
         <v>0.98705499999999802</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -7321,7 +7435,7 @@
         <v>13.322958999999855</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -7339,7 +7453,7 @@
         <v>0.44869200000005094</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -7357,7 +7471,7 @@
         <v>4.8184669999999983</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -7375,7 +7489,7 @@
         <v>0.2845329999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -7393,7 +7507,7 @@
         <v>2.8819950000000176</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -7411,7 +7525,7 @@
         <v>2.97352699999999</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -7429,7 +7543,7 @@
         <v>-4.3905999999999779E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -7447,7 +7561,7 @@
         <v>1.3238649999999978</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -7465,7 +7579,7 @@
         <v>2.2727029999999786</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -7483,7 +7597,7 @@
         <v>5.7754539999999963</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -7501,7 +7615,7 @@
         <v>-1.8117300000000114</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -7519,7 +7633,7 @@
         <v>1.5044249999999977</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -7537,7 +7651,7 @@
         <v>5.9457239999999842</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -7555,7 +7669,7 @@
         <v>4.2056269999999927</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -7573,7 +7687,7 @@
         <v>-9.8579999999999224E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -7591,7 +7705,7 @@
         <v>0.50108300000000128</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -7609,7 +7723,7 @@
         <v>2.5646959999999979</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -7627,7 +7741,7 @@
         <v>-2.251246000000009</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -7645,7 +7759,7 @@
         <v>-0.43250600000010309</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -7663,7 +7777,7 @@
         <v>1.314013000000017</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -7681,7 +7795,7 @@
         <v>-0.24590100000000348</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -7699,7 +7813,7 @@
         <v>1.8975719999999967</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -7717,7 +7831,7 @@
         <v>0.39409200000000055</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -7735,7 +7849,7 @@
         <v>2.0751360000000005</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -7753,7 +7867,7 @@
         <v>-0.68272400000000744</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -7771,7 +7885,7 @@
         <v>0.72619900000000825</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -7789,7 +7903,7 @@
         <v>9.9733889999999406</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -7807,7 +7921,7 @@
         <v>3.1737310000000036</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -7825,7 +7939,7 @@
         <v>1.1315120000000007</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -7843,7 +7957,7 @@
         <v>4.027356999999995</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -7861,7 +7975,7 @@
         <v>13.847968000000037</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -7879,7 +7993,7 @@
         <v>16.309984000000213</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -7897,7 +8011,7 @@
         <v>2.7415500000000179</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -7915,7 +8029,7 @@
         <v>5.9304309999999987</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -7931,6 +8045,24 @@
       <c r="G68">
         <f t="shared" ref="G68" si="1">E68-B68</f>
         <v>2.0829689999999914</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B70">
+        <f>SUM(B3:B68)</f>
+        <v>23856.274812</v>
+      </c>
+      <c r="E70">
+        <f>SUM(E3:E68)</f>
+        <v>24094.682000000001</v>
+      </c>
+      <c r="G70">
+        <f>SUM(G3:G68)</f>
+        <v>238.40718800000002</v>
+      </c>
+      <c r="H70" s="1">
+        <f>G70/B70</f>
+        <v>9.9934792786708793E-3</v>
       </c>
     </row>
   </sheetData>
